--- a/AAII_Financials/Quarterly/LYFT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LYFT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>LYFT</t>
   </si>
@@ -656,511 +656,524 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1843500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1650500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1592700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1685200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1588200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1450200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1550300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1522700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1435800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1277200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1224600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1157600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1020900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1175000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1053800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>990700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>875600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>969900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>864400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>765000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>609000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>569900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>499700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>339300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>955700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1017100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>955600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>867300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>776000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>669600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>585000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>504900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>397200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>344600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>303500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>238900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>172800</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1055100</v>
+      </c>
+      <c r="E9" s="3">
         <v>988500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1095000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1058600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1053200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>969200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>980800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>971500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>935300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>858400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>845800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>763300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>701100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>633700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>895100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>689900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>755700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>538900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>661000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>501900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>420500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>501000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>488400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>384800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>337100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>613700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>649900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>730500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>782100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>650100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>485600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>415100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>360600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>320500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>264000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>237300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>187000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>154800</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>788400</v>
+      </c>
+      <c r="E10" s="3">
         <v>662000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>497700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>626600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>535000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>481000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>569400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>551200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>418800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>378800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>394300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>319800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>366800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>279900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>363900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>235000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>336700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>308900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>362500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>344500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>108000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>81500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>115000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>342000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>367200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>225100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>85200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>125900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>184000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>169900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>144300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>76700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>80600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>66200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>51900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1201,124 +1214,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>119200</v>
+      </c>
+      <c r="E12" s="3">
         <v>124200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>120000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>109600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>109300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>112500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>92600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>104400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>98800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>95200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>109200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>128800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>194400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>234600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>227700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>201800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>192800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>195000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>226700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>252000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>238200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>215200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>232100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>191400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>258700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>276600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>288300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>309800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>631000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>96100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>77200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>64400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>63200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>47700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>37200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>28200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1433,59 +1450,62 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>6900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>34200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
         <v>-5100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>63400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>135700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1495,27 +1515,27 @@
       <c r="V14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X14" s="3">
         <v>21300</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2200</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>35300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>65100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1531,8 +1551,8 @@
       <c r="AH14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1549,53 +1569,56 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E15" s="3">
         <v>36600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>37300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>33600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>23100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>37700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>30200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>30500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>27600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1665,8 +1688,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1704,240 +1730,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1796000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1655800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1770800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1654700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1585800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1479000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1519000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1545200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1463100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1340200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1278500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1197700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1116100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1192900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1771000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1479900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1363900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1074900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1243600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1069400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1005100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1025400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1023300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>953100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>826800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1369800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1398900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1446500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1540200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1932900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>939600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>853600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>698500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>642600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>592000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>503100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>369500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>303500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-178100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>31300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-63000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-53900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-40200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-95200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-192300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-596000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-426100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-373200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-199300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-273700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-205000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-240100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-416400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-453400</v>
       </c>
       <c r="Z18" s="3">
         <v>-453400</v>
       </c>
       <c r="AA18" s="3">
+        <v>-453400</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-487500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-414100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-381800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-490900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-672900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1156900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-270000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-268600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-193600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-245400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-247400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-199600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-130600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-130700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1978,229 +2011,233 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>125000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>19200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>23800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>29300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>29600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>19800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>20600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>20000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>11400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>7800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E21" s="3">
         <v>29400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-134100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>56700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>50300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-33200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-48900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-161800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-522600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-380700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-343100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-157800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-234800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-42900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-203800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-378400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-412800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-404200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-430900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-359500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-333900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-431400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-612200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1114000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-246100</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-232800</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AL21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2210,89 +2247,92 @@
       <c r="AN21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E22" s="3">
         <v>5200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>6200</v>
       </c>
       <c r="O22" s="3">
         <v>6200</v>
       </c>
       <c r="P22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>5000</v>
       </c>
       <c r="S22" s="3">
         <v>5000</v>
       </c>
       <c r="T22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="U22" s="3">
         <v>4500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>13100</v>
       </c>
       <c r="V22" s="3">
         <v>13100</v>
       </c>
       <c r="W22" s="3">
+        <v>13100</v>
+      </c>
+      <c r="X22" s="3">
         <v>12800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1500</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>16</v>
       </c>
@@ -2305,8 +2345,8 @@
       <c r="AG22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
+      <c r="AH22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
@@ -2326,240 +2366,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E23" s="3">
         <v>19800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-147700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>60500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-111600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-185000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-585800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-421600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-377200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-194100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-281200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-93100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-251200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-425400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-460600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-458400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-481900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-396400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-358000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-461600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-643200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1137100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-249300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-248700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-178700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-233900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-239700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-194100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-126200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-127800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2902700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2700</v>
       </c>
       <c r="P24" s="3">
         <v>2700</v>
       </c>
       <c r="Q24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-44800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100</v>
-      </c>
-      <c r="AL24" s="3">
-        <v>200</v>
       </c>
       <c r="AM24" s="3">
         <v>200</v>
       </c>
       <c r="AN24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AO24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2674,240 +2723,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E26" s="3">
         <v>14300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2755100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>46100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>40300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>61700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-114300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-187600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-588100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-422200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-377200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-196900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-283200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-99700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-251900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-427300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-458200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-459500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-437100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-398100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-463500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-644200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1138500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-248900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-249200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-178900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-234300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-239800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-194200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-126400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-127900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E27" s="3">
         <v>14300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2755100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>46100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>61700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-114300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-187600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-588100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-422200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-377200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-196900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-283200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-99700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-251900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-427300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-458200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-459500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-437100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-398100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-463500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-644200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1138500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-248900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-249200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-178900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-234300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-239800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-194200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-126400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-127900</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3022,8 +3080,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3138,8 +3199,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3254,8 +3318,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3370,240 +3437,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-125000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-23800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-29300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-20600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-11400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E33" s="3">
         <v>14300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2755100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>46100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>61700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-114300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-187600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-588100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-422200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-377200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-196900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-283200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-99700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-251900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-427300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-458200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-459500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-437100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-398100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-463500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-644200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1138500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-248900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-249200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-178900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-234300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-239800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-194200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-126400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-127900</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3718,245 +3794,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E35" s="3">
         <v>14300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2755100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>46100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>61700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-114300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-187600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-588100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-422200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-377200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-196900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-283200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-99700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-251900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-427300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-458200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-459500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-437100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-398100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-463500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-644200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1138500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-248900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-249200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-178900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-234300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-239800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-194200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-126400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-127900</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3997,8 +4082,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4039,101 +4125,102 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1137900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1034900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1132000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1305900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>913800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>985500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>759300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>770300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>604400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>507900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>558600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>590500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>638400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>509600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>281100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>143700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>239300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>214900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>457300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>728400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>484200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>312200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>319700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>424800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>841100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>597900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>358300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>543900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>417400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>329500</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>16</v>
       </c>
@@ -4143,8 +4230,8 @@
       <c r="AJ41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK41" s="3">
-        <v>0</v>
+      <c r="AK41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL41" s="3">
         <v>0</v>
@@ -4155,101 +4242,104 @@
       <c r="AN41" s="3">
         <v>0</v>
       </c>
+      <c r="AO41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>656600</v>
+      </c>
+      <c r="E42" s="3">
         <v>686100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>705200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>686600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>878300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1168500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1225100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1156700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1196000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1157700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1126500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1076100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1059700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1245200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1515700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1639700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1567700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2021700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1796500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1653900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1761300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1925100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1931300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2028600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1934900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2072000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2491800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2572600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2892900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>705400</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>16</v>
       </c>
@@ -4259,8 +4349,8 @@
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK42" s="3">
-        <v>0</v>
+      <c r="AK42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL42" s="3">
         <v>0</v>
@@ -4271,53 +4361,56 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>339800</v>
+      </c>
+      <c r="E43" s="3">
         <v>291300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>383900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>399200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>359900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>341700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>334800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>306300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>283800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>281800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>305200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>303000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>315200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>321100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4387,8 +4480,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4431,8 +4527,8 @@
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4503,32 +4599,35 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>350200</v>
+      </c>
+      <c r="E45" s="3">
         <v>304000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>260000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>220300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>242400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>244200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>202400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4547,57 +4646,57 @@
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R45" s="3">
         <v>786100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>689300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>652400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>699000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>522200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>511000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>357000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>343700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>343100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>299600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>320300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>474900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>397200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>426400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>367500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>345500</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4607,8 +4706,8 @@
       <c r="AJ45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK45" s="3">
-        <v>0</v>
+      <c r="AK45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL45" s="3">
         <v>0</v>
@@ -4619,101 +4718,104 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2859400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2722500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2919500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2995400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2757600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3123900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2950500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2867400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2679900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2548800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2577400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2500200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2479300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2547500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2582900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2472700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2459500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2935600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2776100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2893300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2602600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2581000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2594100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2753100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3096200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3144800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3247400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3542800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1380400</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4723,8 +4825,8 @@
       <c r="AJ46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK46" s="3">
-        <v>0</v>
+      <c r="AK46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL46" s="3">
         <v>0</v>
@@ -4735,76 +4837,79 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E47" s="3">
         <v>47000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>42500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>39300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>39900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>26500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>26400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>26300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>155700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>70200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>80400</v>
-      </c>
-      <c r="V47" s="3">
-        <v>75300</v>
       </c>
       <c r="W47" s="3">
         <v>75300</v>
       </c>
       <c r="X47" s="3">
+        <v>75300</v>
+      </c>
+      <c r="Y47" s="3">
         <v>10700</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>10000</v>
       </c>
       <c r="Z47" s="3">
         <v>10000</v>
@@ -4815,8 +4920,8 @@
       <c r="AB47" s="3">
         <v>10000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>16</v>
+      <c r="AC47" s="3">
+        <v>10000</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>16</v>
@@ -4833,8 +4938,8 @@
       <c r="AH47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AJ47" s="3">
         <v>0</v>
@@ -4851,101 +4956,104 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>594200</v>
+      </c>
+      <c r="E48" s="3">
         <v>598100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>584100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>542700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>544000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>561400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>593300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>567700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>617200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>639500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>564000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>577300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>578200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>534500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>448600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>563500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>582800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>526800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>521600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>557700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>570400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>569300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>589100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>619700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>650700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>668300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>629900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>571900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>485200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>425100</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4955,8 +5063,8 @@
       <c r="AJ48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -4967,101 +5075,104 @@
       <c r="AN48" s="3">
         <v>0</v>
       </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>641700</v>
+      </c>
+      <c r="E49" s="3">
         <v>601400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>618700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>524500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>293500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>290800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>294200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>304600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>306700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>311800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>317300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>318200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>329100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>334000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>337800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>342700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>351400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>228900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>231300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>235400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>240300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>244000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>248500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>254500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>262500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>269300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>241600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>241000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>250500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>259200</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>16</v>
       </c>
@@ -5071,8 +5182,8 @@
       <c r="AJ49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK49" s="3">
-        <v>0</v>
+      <c r="AK49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL49" s="3">
         <v>0</v>
@@ -5083,8 +5194,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5199,8 +5313,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5315,101 +5432,104 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2087100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2020200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1954500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1835300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1730900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1649800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1554200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1480400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1353600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1223000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1065800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1043100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1019700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1087000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1160800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1194900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1208200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1007000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1164500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1062700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1082900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1140900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1237200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1331000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1195000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1479400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1572500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1379400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1291000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1176200</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>16</v>
       </c>
@@ -5419,8 +5539,8 @@
       <c r="AJ52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK52" s="3">
-        <v>0</v>
+      <c r="AK52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL52" s="3">
         <v>0</v>
@@ -5431,8 +5551,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5547,101 +5670,104 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9107500</v>
+      </c>
+      <c r="E54" s="3">
         <v>8890000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9030100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5943000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5369400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5668000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5435100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5263200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4997100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4762400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4564500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4478200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4446200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4529500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4556400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4600200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4757500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4768500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4773900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4824300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4571400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4545800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4679000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4968300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5214400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5571800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5691400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5735200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5704500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3240900</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5651,8 +5777,8 @@
       <c r="AJ54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK54" s="3">
-        <v>0</v>
+      <c r="AK54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL54" s="3">
         <v>0</v>
@@ -5663,8 +5789,11 @@
       <c r="AN54" s="3">
         <v>0</v>
       </c>
+      <c r="AO54" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5705,8 +5834,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5747,101 +5877,102 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E57" s="3">
         <v>114900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>120500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>107400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>98600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>97700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>109300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>104500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>103300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>107800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>90100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>95600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>129500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>127400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>77400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>84100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>26000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>48200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>540500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>38800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>36200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>39400</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5851,8 +5982,8 @@
       <c r="AJ57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK57" s="3">
-        <v>0</v>
+      <c r="AK57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL57" s="3">
         <v>0</v>
@@ -5863,89 +5994,92 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E58" s="3">
         <v>117000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>114400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>112300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>100300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>485000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>485500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>503300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>503400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>99500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>93500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>90600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>85000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>87500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>51300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>50200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>67100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>68500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X58" s="3">
         <v>57400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>53200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>56600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>63900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>72400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>80000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5961,8 +6095,8 @@
       <c r="AH58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -5979,101 +6113,104 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>708900</v>
+      </c>
+      <c r="E59" s="3">
         <v>682700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>621400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>586600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>571800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>512400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>440200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>488800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>491600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>537300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>465800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>497500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>506000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>544100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2973400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2644500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2564800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2413100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2386800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2300600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2156700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2097800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1933800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1955200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1858900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1930700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2412500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2344600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2113100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1712700</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>16</v>
       </c>
@@ -6083,8 +6220,8 @@
       <c r="AJ59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6095,101 +6232,104 @@
       <c r="AN59" s="3">
         <v>0</v>
       </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4880500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4665900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4525800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4135900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3916700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4072900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3880700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3848600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3640800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3119200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2961600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2948900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3020400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3135400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3132600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2784800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2731900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2577200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2516400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2428100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2291500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2220800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2074500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2045200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1979600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2551100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2451400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2380800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2125800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1752100</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>16</v>
       </c>
@@ -6199,8 +6339,8 @@
       <c r="AJ60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK60" s="3">
-        <v>0</v>
+      <c r="AK60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL60" s="3">
         <v>0</v>
@@ -6211,89 +6351,92 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1177500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1172500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1201900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1206500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>708900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>744100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>772400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>738700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>756600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1127700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1034800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1030100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1004500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>974500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>823100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>830600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>826000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>801400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>655200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>662500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>670400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>656400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>650800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>633400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>638700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>102800</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6327,101 +6470,104 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E62" s="3">
         <v>25600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>212100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>219200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>232400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>231900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>261100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>277900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>244800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>259800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>277500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>286700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>299600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>310300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>385900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>364900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>301500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>268400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>16</v>
       </c>
@@ -6431,8 +6577,8 @@
       <c r="AJ62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK62" s="3">
-        <v>0</v>
+      <c r="AK62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL62" s="3">
         <v>0</v>
@@ -6443,8 +6589,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6559,8 +6708,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6675,8 +6827,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6791,101 +6946,104 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6083800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5864000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5756500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5370000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4636700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4829900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4668100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4607400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4419500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4271100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4022900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4009900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4059200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4147500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4167800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3834700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3790300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3610500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3432700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3368400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3206600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3137000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3002800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2965200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2917900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2964300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2837300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2745600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2427300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2020500</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6895,8 +7053,8 @@
       <c r="AJ66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK66" s="3">
-        <v>0</v>
+      <c r="AK66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL66" s="3">
         <v>0</v>
@@ -6907,8 +7065,11 @@
       <c r="AN66" s="3">
         <v>0</v>
       </c>
+      <c r="AO66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6949,8 +7110,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7065,8 +7227,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7181,8 +7346,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7271,11 +7439,11 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>5152000</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -7297,8 +7465,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7413,101 +7584,104 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7349600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7399900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7414100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10169200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10215300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10255600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10258100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10319900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10307400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10312500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10280900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10254600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10242500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10128200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9940600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9352500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8930300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8553000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8362600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8079400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7979700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7727800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7300400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6842300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6382800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5945600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5547600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5191500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4728000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4083800</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>16</v>
       </c>
@@ -7517,8 +7691,8 @@
       <c r="AJ72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK72" s="3">
-        <v>0</v>
+      <c r="AK72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL72" s="3">
         <v>0</v>
@@ -7529,8 +7703,11 @@
       <c r="AN72" s="3">
         <v>0</v>
       </c>
+      <c r="AO72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7645,8 +7822,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7761,8 +7941,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7877,101 +8060,104 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3023600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3025900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3273500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>573000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>732700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>838100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>767000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>655800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>577600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>491300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>541500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>468300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>387000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>382000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>388700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>765500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>967300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1158000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1341200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1455900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1364800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1408900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1676200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2003100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2296600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2607500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2854100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2989500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3277100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-3931600</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7981,8 +8167,8 @@
       <c r="AJ76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK76" s="3">
-        <v>0</v>
+      <c r="AK76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL76" s="3">
         <v>0</v>
@@ -7993,8 +8179,11 @@
       <c r="AN76" s="3">
         <v>0</v>
       </c>
+      <c r="AO76" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8109,245 +8298,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E81" s="3">
         <v>14300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2755100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>46100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>61700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-114300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-187600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-588100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-422200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-377200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-196900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-283200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-99700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-251900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-427300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-458200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-459500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-437100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-398100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-463500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-644200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1138500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-248900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-249200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-178900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-234300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-239800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-194200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-126400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-127900</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8388,112 +8586,113 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E83" s="3">
         <v>33600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>22700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>58000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>35900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>33300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>37100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>34600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>34400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>35700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>41700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>44500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>35500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>24100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>30100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>23100</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI83" s="3">
         <v>2600</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK83" s="3">
-        <v>0</v>
+      <c r="AK83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL83" s="3">
         <v>0</v>
@@ -8504,8 +8703,11 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8620,8 +8822,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8736,8 +8941,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8852,8 +9060,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8968,8 +9179,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9084,112 +9298,115 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>349900</v>
+      </c>
+      <c r="E89" s="3">
         <v>307700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>246200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>291300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>343700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>287200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>153400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>264000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>276200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>156200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-70000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-33600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-26200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-25200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-152300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-26200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>41500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-37600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-79500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-264600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-155600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-751700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-206900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-46200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>15300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-84800</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-36000</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK89" s="3">
-        <v>0</v>
+      <c r="AK89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL89" s="3">
         <v>0</v>
@@ -9200,8 +9417,11 @@
       <c r="AN89" s="3">
         <v>0</v>
       </c>
+      <c r="AO89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9242,112 +9462,113 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-46800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-29100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-23000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-30300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-49700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-60100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-17200</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK91" s="3">
-        <v>0</v>
+      <c r="AK91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL91" s="3">
         <v>0</v>
@@ -9358,8 +9579,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9474,8 +9698,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9590,112 +9817,115 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115400</v>
+      </c>
+      <c r="E94" s="3">
         <v>50800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>90300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-179800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>430600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>65700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-194100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-75100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-242100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-107000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-134100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>391500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>449400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>133500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>29400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>97400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-74200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-305700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>231000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>180600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>161100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>185400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-325500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>92900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>787700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-93100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>199900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2387900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>670300</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI94" s="3">
         <v>251700</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK94" s="3">
-        <v>0</v>
+      <c r="AK94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL94" s="3">
         <v>0</v>
@@ -9706,8 +9936,11 @@
       <c r="AN94" s="3">
         <v>0</v>
       </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9748,8 +9981,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9792,8 +10026,8 @@
       <c r="P96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9864,8 +10098,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9980,8 +10217,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10096,8 +10336,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10212,112 +10455,115 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-162100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-366600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-174200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>187900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-647600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-53600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-35500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-31400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-22700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-55600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-33300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-22000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-29100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-23500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>584600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>18000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2411000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-788200</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI100" s="3">
         <v>39400</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
+      <c r="AK100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL100" s="3">
         <v>0</v>
@@ -10328,112 +10574,115 @@
       <c r="AN100" s="3">
         <v>0</v>
       </c>
+      <c r="AO100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
-      </c>
-      <c r="P101" s="3">
-        <v>100</v>
       </c>
       <c r="Q101" s="3">
         <v>100</v>
       </c>
       <c r="R101" s="3">
+        <v>100</v>
+      </c>
+      <c r="S101" s="3">
         <v>-700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI101" s="3" t="s">
-        <v>16</v>
+      <c r="AH101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
+      <c r="AK101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL101" s="3">
         <v>0</v>
@@ -10444,112 +10693,115 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>163100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>299100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>128200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-95900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>222300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>165600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-117800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-78900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-154900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>266200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>347600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>79500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-30700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>60400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-248500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-341200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>243200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>133300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>57400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-102400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-513100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-74500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>564000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-121200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>143200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>38600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-202600</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI102" s="3">
         <v>255200</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK102" s="3">
-        <v>0</v>
+      <c r="AK102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL102" s="3">
         <v>0</v>
@@ -10558,6 +10810,9 @@
         <v>0</v>
       </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
         <v>0</v>
       </c>
     </row>
